--- a/stock_sisley.xlsx
+++ b/stock_sisley.xlsx
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15378</v>
+        <v>2278</v>
       </c>
       <c r="C2" t="n">
         <v>8900</v>
       </c>
       <c r="D2" t="n">
-        <v>-6478</v>
+        <v>6622</v>
       </c>
     </row>
     <row r="3">
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>460</v>
+        <v>360</v>
       </c>
       <c r="C4" t="n">
         <v>2600</v>
       </c>
       <c r="D4" t="n">
-        <v>2140</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="5">
